--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.20941110559187</v>
+        <v>3.284029304658678</v>
       </c>
       <c r="D2" t="n">
-        <v>20.09285236288453</v>
+        <v>3.265088508968736</v>
       </c>
       <c r="E2" t="n">
-        <v>3.106241641424027</v>
+        <v>0.5047642667314043</v>
       </c>
       <c r="F2" t="n">
-        <v>0.875204367678867</v>
+        <v>0.1422207097478159</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.99692782274381</v>
+        <v>2.27450077119587</v>
       </c>
       <c r="D3" t="n">
-        <v>18.3424436275268</v>
+        <v>2.980647089473105</v>
       </c>
       <c r="E3" t="n">
-        <v>3.106241641424027</v>
+        <v>0.5047642667314043</v>
       </c>
       <c r="F3" t="n">
-        <v>0.875204367678867</v>
+        <v>0.1422207097478159</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
